--- a/docs/project-management/03_Design/hld/Northwind-HLD-Checklist.xlsx
+++ b/docs/project-management/03_Design/hld/Northwind-HLD-Checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d752cb73b61fc091/Desktop/linuxlabs/projectredstone/docs/project-management/03_Design/hld/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{9BA763BF-20B3-4587-9990-9674792B8E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB7BC7FD-1F11-4164-A722-640733CEABAB}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{9BA763BF-20B3-4587-9990-9674792B8E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6387490-00EF-4BAF-88D6-7DC27D297283}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-495" yWindow="2835" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{8FB7D13A-EEDF-4023-A0B8-C9B20F621853}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FB7D13A-EEDF-4023-A0B8-C9B20F621853}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasklist" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>Confirm the HLD scope: all approved BRD/RTM requirements are in scope for architectural consideration, even if implementation happens later.</t>
   </si>
@@ -264,6 +264,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,6 +592,7 @@
   <cols>
     <col min="2" max="2" width="128.85546875" style="3" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -621,6 +626,9 @@
       </c>
       <c r="B3" s="3" t="s">
         <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
